--- a/data/trans_camb/IP16B10-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16B10-Provincia-trans_camb.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -739,7 +739,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -895,7 +895,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-51,29</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-32,52</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 0,0</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-51,29%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-32,52%</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1044,14 +1044,14 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 0,0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Huelva</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-51,29</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-32,52</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-51,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-32,52%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1200,14 +1200,14 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Huelva</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1363,7 +1363,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1373,17 +1373,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,0</t>
         </is>
       </c>
     </row>
@@ -1449,17 +1449,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1534,27 +1534,27 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1610,27 +1610,27 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1690,27 +1690,27 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-33,44</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-15,93</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-8,82</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-15,41</t>
         </is>
       </c>
     </row>
@@ -1728,12 +1728,12 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 0,0</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-60,84; 0,0</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-37,68; 0,0</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-65,77; 0,0</t>
         </is>
       </c>
     </row>
@@ -1766,27 +1766,27 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-33,44%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-15,93%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-8,82%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-15,41%</t>
         </is>
       </c>
     </row>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 0,0</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-60,84; 0,0</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -1819,183 +1819,26 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-37,68; 0,0</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-65,77; 0,0</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>-33,44</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-15,93</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>-8,82</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>-15,41</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n"/>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 0,0</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>-66,74; 0,0</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>-37,2; 0,0</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>-74,19; 0,0</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n"/>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>-33,44%</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-15,93%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>-8,82%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>-15,41%</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="n"/>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 0,0</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>-66,74; 0,0</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>-37,2; 0,0</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>-74,19; 0,0</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="12">
     <mergeCell ref="A32:A35"/>
     <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A36:A39"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="G1:H1"/>

--- a/data/trans_camb/IP16B10-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16B10-Provincia-trans_camb.xlsx
@@ -1733,7 +1733,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-60,84; 0,0</t>
+          <t>-62,93; 0,0</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-37,68; 0,0</t>
+          <t>-40,62; 0,0</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-65,77; 0,0</t>
+          <t>-65,3; 0,0</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-60,84; 0,0</t>
+          <t>-62,93; 0,0</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -1819,12 +1819,12 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-37,68; 0,0</t>
+          <t>-40,62; 0,0</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-65,77; 0,0</t>
+          <t>-65,3; 0,0</t>
         </is>
       </c>
     </row>
